--- a/site/User-Actions-on-Integrations/headings.xlsx
+++ b/site/User-Actions-on-Integrations/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>View Script</t>
+          <t>Show Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Set Log Levels</t>
+          <t>References</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,32 +737,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01J0XJ21P9NJ91PY2NQKYVGRBF</t>
+          <t>h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#01J0XJ21P9NJ91PY2NQKYVGRBF</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>h_01H02H9WB603XRNADRN1EK60SB</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
